--- a/assessment_training_forms/012_software_deployment_knowledge_quiz--assessment_training_forms.xlsx
+++ b/assessment_training_forms/012_software_deployment_knowledge_quiz--assessment_training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'agile'}</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Agile'}</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vcs'}</t>
+          <t>vcs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'VCS'}</t>
+          <t>VCS</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ci/cd'}</t>
+          <t>ci/cd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'CI/CD'}</t>
+          <t>CI/CD</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'documentation'}</t>
+          <t>documentation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Documentation'}</t>
+          <t>Documentation</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mentorship'}</t>
+          <t>mentorship</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mentorship'}</t>
+          <t>Mentorship</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
